--- a/artfynd/A 7344-2025 artfynd.xlsx
+++ b/artfynd/A 7344-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16843455</v>
+        <v>16843461</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553445.7241030512</v>
+        <v>553446</v>
       </c>
       <c r="R2" t="n">
-        <v>6271981.878999593</v>
+        <v>6271982</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,21 +743,11 @@
           <t>2014-10-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-10-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -775,6 +760,11 @@
       <c r="AI2" t="inlineStr">
         <is>
           <t>Lövskogsbryn</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>block</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16843461</v>
+        <v>90736452</v>
       </c>
       <c r="B3" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +793,49 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>100045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>sträckande S</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vänsjö, 375 m VNV, Sm</t>
+          <t>Anebo, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553445.7241030512</v>
+        <v>553458</v>
       </c>
       <c r="R3" t="n">
-        <v>6271981.878999593</v>
+        <v>6271990</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +859,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2021-02-05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På 75m höjd snabbt mot S</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,29 +890,769 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Lövskogsbryn</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>block</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tommy Knutsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>93041166</v>
+      </c>
+      <c r="B4" t="n">
+        <v>107609</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hemsjön, 670 m VNV, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>553463</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6271951</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>RIk ädellövskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>93041270</v>
+      </c>
+      <c r="B5" t="n">
+        <v>107609</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vänsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>553421</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6271984</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-04-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Rik ädellövskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>78673941</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vänsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>553421</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6271984</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Lövbryn</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eric Lundén, Tommy Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>78673946</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vänsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>553421</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6271984</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövbryn</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Eric Lundén, Tommy Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>16843455</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vänsjö, 375 m VNV, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>553446</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6271982</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Lövskogsbryn</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Crister Albinsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Crister Albinsson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>78673943</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vänsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>553421</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6271984</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-06-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lövbryn</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eric Lundén, Tommy Nilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>91970089</v>
+      </c>
+      <c r="B10" t="n">
+        <v>109135</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>232013</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spretfibbla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hieracium sparsidens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Dahlst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vänsjö, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>553423</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6271968</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Karlslunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-05-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Rik lövskog</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
